--- a/Result/profitability/5321.xlsx
+++ b/Result/profitability/5321.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.25875</v>
+        <v>-0.3537500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>44.74625</v>
+        <v>45.44</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.295</v>
+        <v>-0.43375</v>
       </c>
       <c r="N3" t="n">
-        <v>40.6825</v>
+        <v>41.275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3425</v>
+        <v>-0.42</v>
       </c>
       <c r="N4" t="n">
-        <v>37.0175</v>
+        <v>37.145</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.31625</v>
+        <v>-0.38875</v>
       </c>
       <c r="N5" t="n">
-        <v>32.95</v>
+        <v>32.84625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.33375</v>
+        <v>-0.4037500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>24.945</v>
+        <v>24.8775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3725</v>
+        <v>-0.3975</v>
       </c>
       <c r="N7" t="n">
-        <v>15.04875</v>
+        <v>15.1075</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3200000000000001</v>
+        <v>-0.09375000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>11.19</v>
+        <v>11.5375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>536</v>
+      </c>
+      <c r="D75" t="n">
+        <v>262</v>
+      </c>
+      <c r="E75" t="n">
+        <v>274</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.49125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7637130801687764</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05748552522746064</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8299999999999983</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01597075235712908</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
